--- a/crime_data_cleaned_weather_metrics.xlsx
+++ b/crime_data_cleaned_weather_metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/0a9d723327c4a8f0/Desktop/Thesis File/New folder/progressWEB - Copy/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="53" documentId="11_271D91BED3E0D67503DA3711595ED87656C9EC80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{58AD55EB-F5A7-4EE8-8AB0-92B72DC1BC56}"/>
+  <xr:revisionPtr revIDLastSave="56" documentId="11_271D91BED3E0D67503DA3711595ED87656C9EC80" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22DEED1F-EFE1-4AD3-95BE-2D6F109EA611}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2330,6 +2330,7 @@
   <dimension ref="A1:T341"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="14" customWidth="1"/>
     <col min="3" max="3" width="12.6640625" customWidth="1"/>
     <col min="4" max="4" width="13.33203125" customWidth="1"/>
     <col min="5" max="5" width="12.5546875" customWidth="1"/>
@@ -2340,6 +2341,8 @@
     <col min="10" max="10" width="9.21875" customWidth="1"/>
     <col min="11" max="11" width="10.109375" customWidth="1"/>
     <col min="12" max="12" width="14.77734375" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7" customWidth="1"/>
+    <col min="19" max="19" width="5.21875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.3">
